--- a/docs/evidence/D7-角色一致性/D7-评分工作簿-五维.xlsx
+++ b/docs/evidence/D7-角色一致性/D7-评分工作簿-五维.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="D7评分" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D7评分" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,13 +529,21 @@
           <t>评审人</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>二 科</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>评分日期</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -637,24 +645,38 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
       <c r="M6" s="6">
         <f>IF(L6="不通过","不通过（合规一票否决）",IF(OR(F6="",G6="",H6="",I6="",J6="",K6="",L6=""),"待填",IF(OR(L6&lt;&gt;"通过",COUNT(G6:J6)&lt;4,AND(F6="是",NOT(ISNUMBER(K6))),AND(F6="否",K6&lt;&gt;"不适用"),COUNTIF(G6:K6,"&gt;3")&gt;0,COUNTIF(G6:K6,"&lt;1")&gt;0),"填写有误",IF(AND(COUNTIF(G6:K6,1)=0,AVERAGE(G6:K6)&gt;=2),"通过","不通过"))))</f>
         <v/>
       </c>
-      <c r="N6" s="5" t="n"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>合规不通过：第5镜女孩用毯子把猫头整个盖住（提示词只写盖在猫身上，原片如此，非合成问题）；第4镜猫眼变绿（定妆图为琥珀色）、猫头抽动两下；第3镜女孩开头只露出一部分、隔雨玻璃偏软。 2026-10-11 后配了旁白台词和烧录字幕，见 final-vo.mp4。</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -674,30 +696,48 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>未生成</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>已有成片</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>kling-v3-omni 1080P + Seedream 5.0 Pro（2026-10-11）</t>
+        </is>
+      </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M7" s="6">
         <f>IF(L7="不通过","不通过（合规一票否决）",IF(OR(F7="",G7="",H7="",I7="",J7="",K7="",L7=""),"待填",IF(OR(L7&lt;&gt;"通过",COUNT(G7:J7)&lt;4,AND(F7="是",NOT(ISNUMBER(K7))),AND(F7="否",K7&lt;&gt;"不适用"),COUNTIF(G7:K7,"&gt;3")&gt;0,COUNTIF(G7:K7,"&lt;1")&gt;0),"填写有误",IF(AND(COUNTIF(G7:K7,1)=0,AVERAGE(G7:K7)&gt;=2),"通过","不通过"))))</f>
         <v/>
       </c>
-      <c r="N7" s="5" t="n"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>第1镜机器人太小；第4镜约2.7s起地面沙石滑动像融化；第5镜近乎静止、偏暗偏软、机器人偏左且颜色变冷（以上来自逐镜检查） 2026-10-11 后配了旁白台词和烧录字幕，见 final-vo.mp4。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -717,30 +757,48 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>未生成</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>已有成片</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>kling-v3-omni 1080P + Seedream 5.0 Pro（2026-10-11）</t>
+        </is>
+      </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M8" s="6">
         <f>IF(L8="不通过","不通过（合规一票否决）",IF(OR(F8="",G8="",H8="",I8="",J8="",K8="",L8=""),"待填",IF(OR(L8&lt;&gt;"通过",COUNT(G8:J8)&lt;4,AND(F8="是",NOT(ISNUMBER(K8))),AND(F8="否",K8&lt;&gt;"不适用"),COUNTIF(G8:K8,"&gt;3")&gt;0,COUNTIF(G8:K8,"&lt;1")&gt;0),"填写有误",IF(AND(COUNTIF(G8:K8,1)=0,AVERAGE(G8:K8)&gt;=2),"通过","不通过"))))</f>
         <v/>
       </c>
-      <c r="N8" s="5" t="n"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>第2镜跑偏：街上撑开伞走进另一家店；第3镜4把伞且伞尖立着、背景与第1镜不一致；第4镜背景为纯灰；第5镜鱼眼变形、首秒近黑、招牌乱码、运镜方向相反（第1–4镜为第一轮生成，第5镜为复用后补） 2026-10-11 后配了旁白台词和烧录字幕，见 final-vo.mp4。</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -760,30 +818,48 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>未生成</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+          <t>已有成片</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>kling-v3-omni 1080P + Seedream 5.0 Pro（2026-10-11）</t>
+        </is>
+      </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M9" s="6">
         <f>IF(L9="不通过","不通过（合规一票否决）",IF(OR(F9="",G9="",H9="",I9="",J9="",K9="",L9=""),"待填",IF(OR(L9&lt;&gt;"通过",COUNT(G9:J9)&lt;4,AND(F9="是",NOT(ISNUMBER(K9))),AND(F9="否",K9&lt;&gt;"不适用"),COUNTIF(G9:K9,"&gt;3")&gt;0,COUNTIF(G9:K9,"&lt;1")&gt;0),"填写有误",IF(AND(COUNTIF(G9:K9,1)=0,AVERAGE(G9:K9)&gt;=2),"通过","不通过"))))</f>
         <v/>
       </c>
-      <c r="N9" s="5" t="n"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>第2镜狐狸背对镜头走、边缘竹子扭曲；第3镜站起两腿走路（定妆图即为站立狐狸）；第4镜茶壶冒黑烟；第5镜仍是黄昏、灯笼一开始就亮、运镜推近而非拉远、狐狸约1s凭空出现（以上来自逐镜检查） 2026-10-11 后配了旁白台词和烧录字幕，见 final-vo.mp4。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -803,30 +879,48 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>未生成</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
+          <t>已有成片</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>kling-v3-omni 1080P + Seedream 5.0 Pro（2026-10-11）</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M10" s="6">
         <f>IF(L10="不通过","不通过（合规一票否决）",IF(OR(F10="",G10="",H10="",I10="",J10="",K10="",L10=""),"待填",IF(OR(L10&lt;&gt;"通过",COUNT(G10:J10)&lt;4,AND(F10="是",NOT(ISNUMBER(K10))),AND(F10="否",K10&lt;&gt;"不适用"),COUNTIF(G10:K10,"&gt;3")&gt;0,COUNTIF(G10:K10,"&lt;1")&gt;0),"填写有误",IF(AND(COUNTIF(G10:K10,1)=0,AVERAGE(G10:K10)&gt;=2),"通过","不通过"))))</f>
         <v/>
       </c>
-      <c r="N10" s="5" t="n"/>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>用户评：骑手像倒着骑车；开盒后是空的，人物干等很久；鹅毛不是从盒里出来而是不知哪里飘出；剧情莫名其妙。逐镜检查：第2、3镜出现两只鹅且整只鹅坐在箱内；第2镜白天与第1镜雨夜不连贯；第3镜开头车被右边缘切掉；第4镜头盔变古铜色（应为银色）。 2026-10-11 后配了旁白台词和烧录字幕，见 final-vo.mp4。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
